--- a/bw_amr_ig/StructureDefinition-botswana-amr-encounter.xlsx
+++ b/bw_amr_ig/StructureDefinition-botswana-amr-encounter.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T15:05:11-04:00</t>
+    <t>2026-03-13T15:54:56-04:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/bw_amr_ig/StructureDefinition-botswana-amr-encounter.xlsx
+++ b/bw_amr_ig/StructureDefinition-botswana-amr-encounter.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2960" uniqueCount="507">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2675" uniqueCount="467">
   <si>
     <t>Property</t>
   </si>
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://bw.health.gov/fhir/ImplementationGuide/bw-amr-ig/StructureDefinition/botswana-amr-encounter</t>
+    <t>http://bw.health.gov/fhir/amr/StructureDefinition/botswana-amr-encounter</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T15:54:56-04:00</t>
+    <t>2026-03-13T21:27:21-04:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -324,22 +324,110 @@
 </t>
   </si>
   <si>
-    <t>Encounter.meta.id</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>Encounter.meta.extension</t>
+    <t>Encounter.implicitRules</t>
+  </si>
+  <si>
+    <t xml:space="preserve">uri
+</t>
+  </si>
+  <si>
+    <t>A set of rules under which this content was created</t>
+  </si>
+  <si>
+    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
+  </si>
+  <si>
+    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
+  </si>
+  <si>
+    <t>Resource.implicitRules</t>
+  </si>
+  <si>
+    <t>Encounter.language</t>
+  </si>
+  <si>
+    <t xml:space="preserve">code
+</t>
+  </si>
+  <si>
+    <t>Language of the resource content</t>
+  </si>
+  <si>
+    <t>The base language in which the resource is written.</t>
+  </si>
+  <si>
+    <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
+  </si>
+  <si>
+    <t>preferred</t>
+  </si>
+  <si>
+    <t>IETF language tag</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.3.0</t>
+  </si>
+  <si>
+    <t>Resource.language</t>
+  </si>
+  <si>
+    <t>Encounter.text</t>
+  </si>
+  <si>
+    <t>narrative
+htmlxhtmldisplay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Narrative
+</t>
+  </si>
+  <si>
+    <t>Text summary of the resource, for human interpretation</t>
+  </si>
+  <si>
+    <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
+  </si>
+  <si>
+    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
+  </si>
+  <si>
+    <t>DomainResource.text</t>
+  </si>
+  <si>
+    <t>Act.text?</t>
+  </si>
+  <si>
+    <t>Encounter.contained</t>
+  </si>
+  <si>
+    <t>inline resources
+anonymous resourcescontained resources</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resource
+</t>
+  </si>
+  <si>
+    <t>Contained, inline Resources</t>
+  </si>
+  <si>
+    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
+  </si>
+  <si>
+    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
+  </si>
+  <si>
+    <t>DomainResource.contained</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dom-r4b:Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
+</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Encounter.extension</t>
   </si>
   <si>
     <t>extensions
@@ -353,409 +441,194 @@
     <t>Additional content defined by implementations</t>
   </si>
   <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
     <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
+    <t>DomainResource.extension</t>
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
-    <t>Encounter.meta.versionId</t>
-  </si>
-  <si>
-    <t>Version specific identifier</t>
-  </si>
-  <si>
-    <t>The version specific identifier, as it appears in the version portion of the URL. This value changes when the resource is created, updated, or deleted.</t>
-  </si>
-  <si>
-    <t>The server assigns this value, and ignores what the client specifies, except in the case that the server is imposing version integrity on updates/deletes.</t>
-  </si>
-  <si>
-    <t>Meta.versionId</t>
-  </si>
-  <si>
-    <t>Encounter.meta.lastUpdated</t>
-  </si>
-  <si>
-    <t xml:space="preserve">instant
+    <t>Encounter.modifierExtension</t>
+  </si>
+  <si>
+    <t>Extensions that cannot be ignored</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
+  </si>
+  <si>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
+  </si>
+  <si>
+    <t>DomainResource.modifierExtension</t>
+  </si>
+  <si>
+    <t>Encounter.identifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identifier
 </t>
   </si>
   <si>
-    <t>When the resource version last changed</t>
-  </si>
-  <si>
-    <t>When the resource last changed - e.g. when the version changed.</t>
-  </si>
-  <si>
-    <t>This value is always populated except when the resource is first being created. The server / resource manager sets this value; what a client provides is irrelevant. This is equivalent to the HTTP Last-Modified and SHOULD have the same value on a [read](http://hl7.org/fhir/R4B/http.html#read) interaction.</t>
-  </si>
-  <si>
-    <t>Meta.lastUpdated</t>
-  </si>
-  <si>
-    <t>Encounter.meta.source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">uri
+    <t>Identifier(s) by which this encounter is known</t>
+  </si>
+  <si>
+    <t>Identifier(s) by which this encounter is known.</t>
+  </si>
+  <si>
+    <t>Event.identifier</t>
+  </si>
+  <si>
+    <t>.id</t>
+  </si>
+  <si>
+    <t>FiveWs.identifier</t>
+  </si>
+  <si>
+    <t>PV1-19</t>
+  </si>
+  <si>
+    <t>Encounter.status</t>
+  </si>
+  <si>
+    <t>planned | arrived | triaged | in-progress | onleave | finished | cancelled +</t>
+  </si>
+  <si>
+    <t>planned | arrived | triaged | in-progress | onleave | finished | cancelled +.</t>
+  </si>
+  <si>
+    <t>Note that internal business rules will determine the appropriate transitions that may occur between statuses (and also classes).</t>
+  </si>
+  <si>
+    <t>finished</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>Current state of the encounter.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/encounter-status|4.3.0</t>
+  </si>
+  <si>
+    <t>Event.status</t>
+  </si>
+  <si>
+    <t>.statusCode</t>
+  </si>
+  <si>
+    <t>FiveWs.status</t>
+  </si>
+  <si>
+    <t>No clear equivalent in HL7 v2; active/finished could be inferred from PV1-44, PV1-45, PV2-24; inactive could be inferred from PV2-16</t>
+  </si>
+  <si>
+    <t>Encounter.statusHistory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BackboneElement
 </t>
   </si>
   <si>
-    <t>Identifies where the resource comes from</t>
-  </si>
-  <si>
-    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4B/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
-  </si>
-  <si>
-    <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
-This element can be used to indicate where the current master source of a resource that has a canonical URL if the resource is no longer hosted at the canonical URL.</t>
-  </si>
-  <si>
-    <t>Meta.source</t>
-  </si>
-  <si>
-    <t>Encounter.meta.profile</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canonical(StructureDefinition|4.3.0)
+    <t>List of past encounter statuses</t>
+  </si>
+  <si>
+    <t>The status history permits the encounter resource to contain the status history without needing to read through the historical versions of the resource, or even have the server store them.</t>
+  </si>
+  <si>
+    <t>The current status is always found in the current version of the resource, not the status history.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
 </t>
   </si>
   <si>
-    <t>Profiles this resource claims to conform to</t>
-  </si>
-  <si>
-    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4B/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4B/structuredefinition-definitions.html#StructureDefinition.url).</t>
-  </si>
-  <si>
-    <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
-  </si>
-  <si>
-    <t>http://bw.health.gov/fhir/StructureDefinition/BotswanaAMR-Encounter</t>
-  </si>
-  <si>
-    <t>Meta.profile</t>
-  </si>
-  <si>
-    <t>Encounter.meta.security</t>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Encounter.statusHistory.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>Encounter.statusHistory.extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Encounter.statusHistory.modifierExtension</t>
+  </si>
+  <si>
+    <t>extensions
+user contentmodifiers</t>
+  </si>
+  <si>
+    <t>Extensions that cannot be ignored even if unrecognized</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
+  </si>
+  <si>
+    <t>BackboneElement.modifierExtension</t>
+  </si>
+  <si>
+    <t>Encounter.statusHistory.status</t>
+  </si>
+  <si>
+    <t>Encounter.statusHistory.period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Period
+</t>
+  </si>
+  <si>
+    <t>The time that the episode was in the specified status</t>
+  </si>
+  <si>
+    <t>The time that the episode was in the specified status.</t>
+  </si>
+  <si>
+    <t>Encounter.class</t>
   </si>
   <si>
     <t xml:space="preserve">Coding
 </t>
   </si>
   <si>
-    <t>Security Labels applied to this resource</t>
-  </si>
-  <si>
-    <t>Security labels applied to this resource. These tags connect specific resources to the overall security policy and infrastructure.</t>
-  </si>
-  <si>
-    <t>The security labels can be updated without changing the stated version of the resource. The list of security labels is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+    <t>Classification of patient encounter</t>
+  </si>
+  <si>
+    <t>Concepts representing classification of patient encounter such as ambulatory (outpatient), inpatient, emergency, home health or others due to local variations.</t>
   </si>
   <si>
     <t>extensible</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels|4.3.0</t>
-  </si>
-  <si>
-    <t>Meta.security</t>
-  </si>
-  <si>
-    <t>Encounter.meta.tag</t>
-  </si>
-  <si>
-    <t>Tags applied to this resource</t>
-  </si>
-  <si>
-    <t>Tags applied to this resource. Tags are intended to be used to identify and relate resources to process and workflow, and applications are not required to consider the tags when interpreting the meaning of a resource.</t>
-  </si>
-  <si>
-    <t>The tags can be updated without changing the stated version of the resource. The list of tags is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
-  </si>
-  <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags|4.3.0</t>
-  </si>
-  <si>
-    <t>Meta.tag</t>
-  </si>
-  <si>
-    <t>Encounter.implicitRules</t>
-  </si>
-  <si>
-    <t>A set of rules under which this content was created</t>
-  </si>
-  <si>
-    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
-  </si>
-  <si>
-    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
-  </si>
-  <si>
-    <t>Resource.implicitRules</t>
-  </si>
-  <si>
-    <t>Encounter.language</t>
-  </si>
-  <si>
-    <t xml:space="preserve">code
-</t>
-  </si>
-  <si>
-    <t>Language of the resource content</t>
-  </si>
-  <si>
-    <t>The base language in which the resource is written.</t>
-  </si>
-  <si>
-    <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
-  </si>
-  <si>
-    <t>preferred</t>
-  </si>
-  <si>
-    <t>IETF language tag</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/languages|4.3.0</t>
-  </si>
-  <si>
-    <t>Resource.language</t>
-  </si>
-  <si>
-    <t>Encounter.text</t>
-  </si>
-  <si>
-    <t>narrative
-htmlxhtmldisplay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Narrative
-</t>
-  </si>
-  <si>
-    <t>Text summary of the resource, for human interpretation</t>
-  </si>
-  <si>
-    <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
-  </si>
-  <si>
-    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
-  </si>
-  <si>
-    <t>DomainResource.text</t>
-  </si>
-  <si>
-    <t>Act.text?</t>
-  </si>
-  <si>
-    <t>Encounter.contained</t>
-  </si>
-  <si>
-    <t>inline resources
-anonymous resourcescontained resources</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Resource
-</t>
-  </si>
-  <si>
-    <t>Contained, inline Resources</t>
-  </si>
-  <si>
-    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
-  </si>
-  <si>
-    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
-  </si>
-  <si>
-    <t>DomainResource.contained</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dom-r4b:Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
-</t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>Encounter.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>Encounter.modifierExtension</t>
-  </si>
-  <si>
-    <t>Extensions that cannot be ignored</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
-Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
-  </si>
-  <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
-  </si>
-  <si>
-    <t>DomainResource.modifierExtension</t>
-  </si>
-  <si>
-    <t>Encounter.identifier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Identifier
-</t>
-  </si>
-  <si>
-    <t>Identifier(s) by which this encounter is known</t>
-  </si>
-  <si>
-    <t>Identifier(s) by which this encounter is known.</t>
-  </si>
-  <si>
-    <t>Event.identifier</t>
-  </si>
-  <si>
-    <t>.id</t>
-  </si>
-  <si>
-    <t>FiveWs.identifier</t>
-  </si>
-  <si>
-    <t>PV1-19</t>
-  </si>
-  <si>
-    <t>Encounter.status</t>
-  </si>
-  <si>
-    <t>planned | arrived | triaged | in-progress | onleave | finished | cancelled +</t>
-  </si>
-  <si>
-    <t>planned | arrived | triaged | in-progress | onleave | finished | cancelled +.</t>
-  </si>
-  <si>
-    <t>Note that internal business rules will determine the appropriate transitions that may occur between statuses (and also classes).</t>
-  </si>
-  <si>
-    <t>finished</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>Current state of the encounter.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/encounter-status|4.3.0</t>
-  </si>
-  <si>
-    <t>Event.status</t>
-  </si>
-  <si>
-    <t>.statusCode</t>
-  </si>
-  <si>
-    <t>FiveWs.status</t>
-  </si>
-  <si>
-    <t>No clear equivalent in HL7 v2; active/finished could be inferred from PV1-44, PV1-45, PV2-24; inactive could be inferred from PV2-16</t>
-  </si>
-  <si>
-    <t>Encounter.statusHistory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BackboneElement
-</t>
-  </si>
-  <si>
-    <t>List of past encounter statuses</t>
-  </si>
-  <si>
-    <t>The status history permits the encounter resource to contain the status history without needing to read through the historical versions of the resource, or even have the server store them.</t>
-  </si>
-  <si>
-    <t>The current status is always found in the current version of the resource, not the status history.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
-</t>
-  </si>
-  <si>
-    <t>Encounter.statusHistory.id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Encounter.statusHistory.extension</t>
-  </si>
-  <si>
-    <t>Encounter.statusHistory.modifierExtension</t>
-  </si>
-  <si>
-    <t>extensions
-user contentmodifiers</t>
-  </si>
-  <si>
-    <t>Extensions that cannot be ignored even if unrecognized</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
-Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
-  </si>
-  <si>
-    <t>BackboneElement.modifierExtension</t>
-  </si>
-  <si>
-    <t>Encounter.statusHistory.status</t>
-  </si>
-  <si>
-    <t>Encounter.statusHistory.period</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Period
-</t>
-  </si>
-  <si>
-    <t>The time that the episode was in the specified status</t>
-  </si>
-  <si>
-    <t>The time that the episode was in the specified status.</t>
-  </si>
-  <si>
-    <t>Encounter.class</t>
-  </si>
-  <si>
-    <t>Classification of patient encounter</t>
-  </si>
-  <si>
-    <t>Concepts representing classification of patient encounter such as ambulatory (outpatient), inpatient, emergency, home health or others due to local variations.</t>
-  </si>
-  <si>
-    <t>http://bw.health.gov/fhir/ImplementationGuide/bw-amr-ig/ValueSet/botswana-amr-ward-type-vs</t>
+    <t>http://bw.health.gov/fhir/amr/ValueSet/botswana-amr-ward-type-vs</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=SUBJ].source[classCode=LIST].code</t>
@@ -825,6 +698,9 @@
     <t>Since there are many ways to further classify encounters, this element is 0..*.</t>
   </si>
   <si>
+    <t>example</t>
+  </si>
+  <si>
     <t>A specific code indicating type of service provided</t>
   </si>
   <si>
@@ -886,7 +762,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://bw.health.gov/fhir/ImplementationGuide/bw-amr-ig/StructureDefinition/botswana-amr-patient)
+    <t xml:space="preserve">Reference(http://bw.health.gov/fhir/amr/StructureDefinition/botswana-amr-patient)
 </t>
   </si>
   <si>
@@ -1888,7 +1764,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN82"/>
+  <dimension ref="A1:AN74"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="41.2421875" customWidth="true" bestFit="true"/>
@@ -1901,7 +1777,7 @@
     <col min="8" max="8" width="13.609375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.1796875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="93.76171875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="85.3984375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1916,10 +1792,10 @@
     <col min="23" max="23" width="16.40625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="15.85546875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="66.58984375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="80.59375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="56.703125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.2734375" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.1171875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="36.56640625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="17.16015625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.3671875" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="11.84375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="41.2421875" customWidth="true" bestFit="true" hidden="true"/>
@@ -2414,21 +2290,23 @@
         <v>20</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N5" s="2"/>
+        <v>104</v>
+      </c>
+      <c r="N5" t="s" s="2">
+        <v>105</v>
+      </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
         <v>20</v>
@@ -2477,7 +2355,7 @@
         <v>20</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>78</v>
@@ -2489,13 +2367,13 @@
         <v>20</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL5" t="s" s="2">
-        <v>105</v>
+        <v>20</v>
       </c>
       <c r="AM5" t="s" s="2">
         <v>20</v>
@@ -2506,21 +2384,21 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>107</v>
+        <v>20</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>20</v>
@@ -2567,28 +2445,28 @@
         <v>20</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>20</v>
+        <v>112</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>20</v>
+        <v>113</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>20</v>
+        <v>114</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AB6" t="s" s="2">
-        <v>112</v>
+        <v>20</v>
       </c>
       <c r="AC6" t="s" s="2">
-        <v>113</v>
+        <v>20</v>
       </c>
       <c r="AD6" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>114</v>
+        <v>20</v>
       </c>
       <c r="AF6" t="s" s="2">
         <v>115</v>
@@ -2597,19 +2475,19 @@
         <v>78</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL6" t="s" s="2">
-        <v>105</v>
+        <v>20</v>
       </c>
       <c r="AM6" t="s" s="2">
         <v>20</v>
@@ -2620,14 +2498,14 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>20</v>
+        <v>117</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
@@ -2643,19 +2521,19 @@
         <v>20</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>90</v>
+        <v>118</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2705,7 +2583,7 @@
         <v>20</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>78</v>
@@ -2723,7 +2601,7 @@
         <v>20</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>20</v>
+        <v>123</v>
       </c>
       <c r="AM7" t="s" s="2">
         <v>20</v>
@@ -2734,21 +2612,21 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>20</v>
+        <v>125</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>20</v>
@@ -2757,19 +2635,19 @@
         <v>20</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2819,25 +2697,25 @@
         <v>20</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>100</v>
+        <v>131</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>20</v>
+        <v>132</v>
       </c>
       <c r="AM8" t="s" s="2">
         <v>20</v>
@@ -2848,21 +2726,21 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>20</v>
+        <v>134</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>20</v>
@@ -2871,19 +2749,19 @@
         <v>20</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2933,25 +2811,25 @@
         <v>20</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>20</v>
+        <v>132</v>
       </c>
       <c r="AM9" t="s" s="2">
         <v>20</v>
@@ -2962,14 +2840,14 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
-        <v>20</v>
+        <v>134</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -2982,24 +2860,26 @@
         <v>20</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K10" t="s" s="2">
         <v>135</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="N10" t="s" s="2">
         <v>138</v>
       </c>
-      <c r="O10" s="2"/>
+      <c r="O10" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="P10" t="s" s="2">
         <v>20</v>
       </c>
@@ -3008,7 +2888,7 @@
         <v>20</v>
       </c>
       <c r="S10" t="s" s="2">
-        <v>139</v>
+        <v>20</v>
       </c>
       <c r="T10" t="s" s="2">
         <v>20</v>
@@ -3047,7 +2927,7 @@
         <v>20</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -3059,13 +2939,13 @@
         <v>20</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>20</v>
+        <v>132</v>
       </c>
       <c r="AM10" t="s" s="2">
         <v>20</v>
@@ -3076,10 +2956,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3102,17 +2982,15 @@
         <v>89</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="N11" t="s" s="2">
-        <v>145</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="N11" s="2"/>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>20</v>
@@ -3137,29 +3015,31 @@
         <v>20</v>
       </c>
       <c r="X11" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y11" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z11" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA11" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB11" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC11" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD11" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE11" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF11" t="s" s="2">
         <v>146</v>
-      </c>
-      <c r="Y11" s="2"/>
-      <c r="Z11" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="AA11" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB11" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC11" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD11" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE11" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF11" t="s" s="2">
-        <v>148</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -3174,24 +3054,24 @@
         <v>100</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>20</v>
+        <v>150</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>20</v>
+        <v>151</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>20</v>
+        <v>152</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>20</v>
+        <v>153</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3199,31 +3079,31 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="J12" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>142</v>
+        <v>108</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -3234,7 +3114,7 @@
         <v>20</v>
       </c>
       <c r="S12" t="s" s="2">
-        <v>20</v>
+        <v>158</v>
       </c>
       <c r="T12" t="s" s="2">
         <v>20</v>
@@ -3249,35 +3129,37 @@
         <v>20</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="Y12" s="2"/>
+        <v>159</v>
+      </c>
+      <c r="Y12" t="s" s="2">
+        <v>160</v>
+      </c>
       <c r="Z12" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AA12" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB12" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC12" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD12" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE12" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF12" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="AA12" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB12" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC12" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD12" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE12" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF12" t="s" s="2">
-        <v>155</v>
-      </c>
       <c r="AG12" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>20</v>
@@ -3286,24 +3168,24 @@
         <v>100</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>20</v>
+        <v>162</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>20</v>
+        <v>163</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>20</v>
+        <v>164</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>20</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3314,28 +3196,28 @@
         <v>78</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>129</v>
+        <v>167</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3385,25 +3267,25 @@
         <v>20</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>100</v>
+        <v>171</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>20</v>
+        <v>172</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>20</v>
@@ -3414,10 +3296,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3440,17 +3322,15 @@
         <v>20</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>165</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="N14" s="2"/>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>20</v>
@@ -3475,13 +3355,13 @@
         <v>20</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>166</v>
+        <v>20</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>167</v>
+        <v>20</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>168</v>
+        <v>20</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>20</v>
@@ -3499,7 +3379,7 @@
         <v>20</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -3511,13 +3391,13 @@
         <v>20</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>20</v>
+        <v>172</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>20</v>
@@ -3528,21 +3408,21 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>171</v>
+        <v>134</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>20</v>
@@ -3554,16 +3434,16 @@
         <v>20</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>172</v>
+        <v>135</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>173</v>
+        <v>136</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>175</v>
+        <v>138</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3613,25 +3493,25 @@
         <v>20</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>20</v>
@@ -3642,14 +3522,14 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3662,24 +3542,26 @@
         <v>20</v>
       </c>
       <c r="I16" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>180</v>
+        <v>135</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="O16" s="2"/>
+        <v>138</v>
+      </c>
+      <c r="O16" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="P16" t="s" s="2">
         <v>20</v>
       </c>
@@ -3727,7 +3609,7 @@
         <v>20</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -3739,13 +3621,13 @@
         <v>20</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>185</v>
+        <v>140</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>186</v>
+        <v>132</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>20</v>
@@ -3756,21 +3638,21 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>107</v>
+        <v>20</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>20</v>
@@ -3785,14 +3667,12 @@
         <v>108</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>109</v>
+        <v>155</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="N17" s="2"/>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>20</v>
@@ -3817,13 +3697,13 @@
         <v>20</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>20</v>
+        <v>159</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>20</v>
+        <v>160</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>20</v>
+        <v>161</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>20</v>
@@ -3841,25 +3721,25 @@
         <v>20</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>186</v>
+        <v>172</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>20</v>
@@ -3870,46 +3750,42 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>107</v>
+        <v>20</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="J18" t="s" s="2">
         <v>20</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>108</v>
+        <v>188</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="O18" t="s" s="2">
-        <v>193</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>20</v>
       </c>
@@ -3957,25 +3833,25 @@
         <v>20</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>186</v>
+        <v>172</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>20</v>
@@ -3986,10 +3862,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3997,10 +3873,10 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>20</v>
@@ -4012,13 +3888,13 @@
         <v>89</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4045,13 +3921,11 @@
         <v>20</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y19" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="Y19" s="2"/>
       <c r="Z19" t="s" s="2">
-        <v>20</v>
+        <v>196</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>20</v>
@@ -4069,13 +3943,13 @@
         <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>20</v>
@@ -4084,24 +3958,24 @@
         <v>100</v>
       </c>
       <c r="AK19" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL19" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="AM19" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="AN19" t="s" s="2">
         <v>199</v>
-      </c>
-      <c r="AL19" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="AM19" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="AN19" t="s" s="2">
-        <v>202</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4109,32 +3983,30 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>206</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>20</v>
@@ -4144,7 +4016,7 @@
         <v>20</v>
       </c>
       <c r="S20" t="s" s="2">
-        <v>207</v>
+        <v>20</v>
       </c>
       <c r="T20" t="s" s="2">
         <v>20</v>
@@ -4159,13 +4031,13 @@
         <v>20</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>208</v>
+        <v>20</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>209</v>
+        <v>20</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>210</v>
+        <v>20</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>20</v>
@@ -4183,39 +4055,39 @@
         <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>100</v>
+        <v>171</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>211</v>
+        <v>20</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>212</v>
+        <v>172</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>213</v>
+        <v>20</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>214</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4226,7 +4098,7 @@
         <v>78</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>20</v>
@@ -4238,17 +4110,15 @@
         <v>20</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>216</v>
+        <v>174</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>217</v>
+        <v>175</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>219</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>20</v>
@@ -4297,25 +4167,25 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>215</v>
+        <v>177</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>220</v>
+        <v>20</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>105</v>
+        <v>172</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>20</v>
@@ -4326,21 +4196,21 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>221</v>
+        <v>204</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>221</v>
+        <v>204</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>20</v>
+        <v>134</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>20</v>
@@ -4352,15 +4222,17 @@
         <v>20</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>222</v>
+        <v>135</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>102</v>
+        <v>136</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N22" s="2"/>
+        <v>179</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>20</v>
@@ -4409,25 +4281,25 @@
         <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>104</v>
+        <v>180</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>20</v>
+        <v>140</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>105</v>
+        <v>172</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>20</v>
@@ -4438,14 +4310,14 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>223</v>
+        <v>205</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>223</v>
+        <v>205</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>107</v>
+        <v>182</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -4458,24 +4330,26 @@
         <v>20</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>108</v>
+        <v>135</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>109</v>
+        <v>183</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>110</v>
+        <v>184</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="O23" s="2"/>
+        <v>138</v>
+      </c>
+      <c r="O23" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="P23" t="s" s="2">
         <v>20</v>
       </c>
@@ -4523,7 +4397,7 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>115</v>
+        <v>185</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4535,13 +4409,13 @@
         <v>20</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>116</v>
+        <v>140</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>105</v>
+        <v>132</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>20</v>
@@ -4552,46 +4426,42 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>224</v>
+        <v>206</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>225</v>
+        <v>20</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>108</v>
+        <v>192</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>226</v>
+        <v>207</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>193</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>20</v>
       </c>
@@ -4615,13 +4485,13 @@
         <v>20</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>20</v>
+        <v>195</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>20</v>
+        <v>209</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>20</v>
+        <v>210</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>20</v>
@@ -4639,25 +4509,25 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>228</v>
+        <v>206</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>186</v>
+        <v>172</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>20</v>
@@ -4668,10 +4538,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>229</v>
+        <v>211</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>229</v>
+        <v>211</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4694,13 +4564,13 @@
         <v>20</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>162</v>
+        <v>188</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4727,13 +4597,13 @@
         <v>20</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>208</v>
+        <v>20</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>209</v>
+        <v>20</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>210</v>
+        <v>20</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>20</v>
@@ -4751,7 +4621,7 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>229</v>
+        <v>211</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>88</v>
@@ -4769,7 +4639,7 @@
         <v>20</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>105</v>
+        <v>172</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>20</v>
@@ -4780,10 +4650,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>230</v>
+        <v>214</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>230</v>
+        <v>214</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4791,10 +4661,10 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>20</v>
@@ -4803,18 +4673,20 @@
         <v>20</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>231</v>
+        <v>215</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>232</v>
+        <v>216</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="N26" s="2"/>
+        <v>217</v>
+      </c>
+      <c r="N26" t="s" s="2">
+        <v>218</v>
+      </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>20</v>
@@ -4839,13 +4711,13 @@
         <v>20</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>20</v>
+        <v>219</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>20</v>
+        <v>220</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>20</v>
+        <v>221</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>20</v>
@@ -4863,13 +4735,13 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>230</v>
+        <v>214</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>20</v>
@@ -4878,24 +4750,24 @@
         <v>100</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>20</v>
+        <v>222</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>105</v>
+        <v>223</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>20</v>
+        <v>198</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>20</v>
+        <v>224</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4903,7 +4775,7 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>88</v>
@@ -4918,13 +4790,13 @@
         <v>89</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>142</v>
+        <v>215</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4951,11 +4823,13 @@
         <v>20</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="Y27" s="2"/>
+        <v>219</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>228</v>
+      </c>
       <c r="Z27" t="s" s="2">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>20</v>
@@ -4973,10 +4847,10 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH27" t="s" s="2">
         <v>88</v>
@@ -4988,24 +4862,24 @@
         <v>100</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>20</v>
+        <v>222</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>238</v>
+        <v>172</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>239</v>
+        <v>20</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>240</v>
+        <v>230</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5016,7 +4890,7 @@
         <v>78</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>20</v>
@@ -5028,13 +4902,13 @@
         <v>20</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5061,13 +4935,13 @@
         <v>20</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>20</v>
+        <v>219</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>20</v>
+        <v>233</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>20</v>
+        <v>234</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>20</v>
@@ -5085,47 +4959,47 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>220</v>
+        <v>100</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>105</v>
+        <v>235</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>20</v>
+        <v>236</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>20</v>
+        <v>237</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>20</v>
+        <v>239</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>88</v>
@@ -5137,18 +5011,20 @@
         <v>20</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>222</v>
+        <v>240</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>102</v>
+        <v>241</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N29" s="2"/>
+        <v>242</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>243</v>
+      </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>20</v>
@@ -5197,7 +5073,7 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>104</v>
+        <v>238</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5209,31 +5085,31 @@
         <v>20</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>20</v>
+        <v>244</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>105</v>
+        <v>245</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>20</v>
+        <v>246</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>20</v>
+        <v>247</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>107</v>
+        <v>20</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5249,20 +5125,18 @@
         <v>20</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>108</v>
+        <v>249</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>109</v>
+        <v>250</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>251</v>
+      </c>
+      <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>20</v>
@@ -5311,7 +5185,7 @@
         <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>115</v>
+        <v>248</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -5323,31 +5197,31 @@
         <v>20</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>20</v>
+        <v>252</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>105</v>
+        <v>172</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>20</v>
+        <v>253</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>20</v>
+        <v>254</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>225</v>
+        <v>256</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -5360,26 +5234,22 @@
         <v>20</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>108</v>
+        <v>257</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>226</v>
+        <v>258</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>193</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>20</v>
       </c>
@@ -5427,7 +5297,7 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>228</v>
+        <v>255</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5439,13 +5309,13 @@
         <v>20</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>20</v>
+        <v>260</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>186</v>
+        <v>261</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>20</v>
@@ -5456,10 +5326,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>247</v>
+        <v>262</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>247</v>
+        <v>262</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5467,10 +5337,10 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>20</v>
@@ -5479,16 +5349,16 @@
         <v>20</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>142</v>
+        <v>167</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>248</v>
+        <v>263</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>249</v>
+        <v>264</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5515,13 +5385,13 @@
         <v>20</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>146</v>
+        <v>20</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>250</v>
+        <v>20</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>251</v>
+        <v>20</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>20</v>
@@ -5539,39 +5409,39 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>247</v>
+        <v>262</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>100</v>
+        <v>171</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>20</v>
+        <v>265</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>105</v>
+        <v>266</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>20</v>
+        <v>267</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>252</v>
+        <v>268</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>252</v>
+        <v>268</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5579,7 +5449,7 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>88</v>
@@ -5594,13 +5464,13 @@
         <v>20</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>231</v>
+        <v>174</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>253</v>
+        <v>175</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>254</v>
+        <v>176</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5651,10 +5521,10 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>252</v>
+        <v>177</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH33" t="s" s="2">
         <v>88</v>
@@ -5663,13 +5533,13 @@
         <v>20</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>105</v>
+        <v>172</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>20</v>
@@ -5680,14 +5550,14 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>255</v>
+        <v>269</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>255</v>
+        <v>269</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>20</v>
+        <v>134</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5703,19 +5573,19 @@
         <v>20</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>256</v>
+        <v>135</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>257</v>
+        <v>136</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>258</v>
+        <v>179</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>259</v>
+        <v>138</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5741,13 +5611,13 @@
         <v>20</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>153</v>
+        <v>20</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>260</v>
+        <v>20</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>261</v>
+        <v>20</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>20</v>
@@ -5765,7 +5635,7 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>255</v>
+        <v>180</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5777,59 +5647,63 @@
         <v>20</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>262</v>
+        <v>20</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>263</v>
+        <v>172</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>239</v>
+        <v>20</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>264</v>
+        <v>20</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>20</v>
+        <v>182</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="J35" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>256</v>
+        <v>135</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>266</v>
+        <v>183</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="N35" s="2"/>
-      <c r="O35" s="2"/>
+        <v>184</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="O35" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="P35" t="s" s="2">
         <v>20</v>
       </c>
@@ -5853,13 +5727,13 @@
         <v>20</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>153</v>
+        <v>20</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>268</v>
+        <v>20</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>269</v>
+        <v>20</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>20</v>
@@ -5877,31 +5751,31 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>265</v>
+        <v>185</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>262</v>
+        <v>20</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>105</v>
+        <v>132</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>270</v>
+        <v>20</v>
       </c>
     </row>
     <row r="36">
@@ -5920,7 +5794,7 @@
         <v>78</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>20</v>
@@ -5929,10 +5803,10 @@
         <v>20</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>256</v>
+        <v>215</v>
       </c>
       <c r="L36" t="s" s="2">
         <v>272</v>
@@ -5940,7 +5814,9 @@
       <c r="M36" t="s" s="2">
         <v>273</v>
       </c>
-      <c r="N36" s="2"/>
+      <c r="N36" t="s" s="2">
+        <v>274</v>
+      </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>20</v>
@@ -5965,13 +5841,13 @@
         <v>20</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>153</v>
+        <v>195</v>
       </c>
       <c r="Y36" t="s" s="2">
         <v>273</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>20</v>
@@ -5995,7 +5871,7 @@
         <v>78</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>20</v>
@@ -6004,32 +5880,32 @@
         <v>100</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>20</v>
+        <v>276</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>276</v>
+        <v>20</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>279</v>
+        <v>20</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>88</v>
@@ -6041,20 +5917,18 @@
         <v>20</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="M37" t="s" s="2">
         <v>281</v>
       </c>
-      <c r="M37" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>283</v>
-      </c>
+      <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>20</v>
@@ -6103,7 +5977,7 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -6118,24 +5992,24 @@
         <v>100</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>284</v>
+        <v>20</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>286</v>
+        <v>20</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>287</v>
+        <v>283</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6146,7 +6020,7 @@
         <v>78</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>20</v>
@@ -6158,13 +6032,13 @@
         <v>89</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6215,13 +6089,13 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>20</v>
@@ -6230,28 +6104,28 @@
         <v>100</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>105</v>
+        <v>289</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>294</v>
+        <v>291</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>296</v>
+        <v>20</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -6267,16 +6141,16 @@
         <v>20</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6327,7 +6201,7 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6342,24 +6216,24 @@
         <v>100</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>300</v>
+        <v>260</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>20</v>
+        <v>297</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6370,7 +6244,7 @@
         <v>78</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>20</v>
@@ -6379,18 +6253,20 @@
         <v>20</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>216</v>
+        <v>188</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="N40" s="2"/>
+        <v>300</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>301</v>
+      </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>20</v>
@@ -6439,39 +6315,39 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AG40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH40" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ40" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK40" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="AG40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH40" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ40" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="AK40" t="s" s="2">
+      <c r="AL40" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="AM40" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="AN40" t="s" s="2">
         <v>305</v>
-      </c>
-      <c r="AL40" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="AM40" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN40" t="s" s="2">
-        <v>307</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6494,15 +6370,17 @@
         <v>20</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>102</v>
+        <v>308</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N41" s="2"/>
+        <v>309</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>310</v>
+      </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>20</v>
@@ -6551,7 +6429,7 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>104</v>
+        <v>306</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6563,31 +6441,31 @@
         <v>20</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>20</v>
+        <v>302</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>105</v>
+        <v>311</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>20</v>
+        <v>312</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>107</v>
+        <v>314</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6603,19 +6481,19 @@
         <v>20</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>108</v>
+        <v>215</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>109</v>
+        <v>315</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>110</v>
+        <v>316</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>111</v>
+        <v>317</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6641,13 +6519,13 @@
         <v>20</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>20</v>
+        <v>112</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>20</v>
+        <v>318</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>20</v>
+        <v>319</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>20</v>
@@ -6665,7 +6543,7 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>115</v>
+        <v>313</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6677,31 +6555,31 @@
         <v>20</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>20</v>
+        <v>320</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>105</v>
+        <v>321</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>20</v>
+        <v>322</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>20</v>
+        <v>323</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>310</v>
+        <v>324</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>310</v>
+        <v>324</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>225</v>
+        <v>314</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6714,26 +6592,24 @@
         <v>20</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="J43" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>108</v>
+        <v>325</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>226</v>
+        <v>326</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>227</v>
+        <v>316</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>193</v>
-      </c>
+        <v>317</v>
+      </c>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>20</v>
       </c>
@@ -6781,7 +6657,7 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>228</v>
+        <v>324</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6793,27 +6669,27 @@
         <v>20</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>20</v>
+        <v>320</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>186</v>
+        <v>321</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>20</v>
+        <v>322</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>20</v>
+        <v>323</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>311</v>
+        <v>327</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>311</v>
+        <v>327</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6836,17 +6712,15 @@
         <v>89</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>256</v>
+        <v>167</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>312</v>
+        <v>328</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>314</v>
-      </c>
+        <v>329</v>
+      </c>
+      <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>20</v>
@@ -6871,13 +6745,13 @@
         <v>20</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>146</v>
+        <v>20</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>313</v>
+        <v>20</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>315</v>
+        <v>20</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>20</v>
@@ -6895,7 +6769,7 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>311</v>
+        <v>327</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -6907,27 +6781,27 @@
         <v>20</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>100</v>
+        <v>171</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>316</v>
+        <v>20</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>317</v>
+        <v>330</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>318</v>
+        <v>20</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>319</v>
+        <v>331</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>319</v>
+        <v>331</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6950,13 +6824,13 @@
         <v>20</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>231</v>
+        <v>174</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>320</v>
+        <v>175</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>321</v>
+        <v>176</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7007,7 +6881,7 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>319</v>
+        <v>177</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -7019,38 +6893,38 @@
         <v>20</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>322</v>
+        <v>172</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>323</v>
+        <v>20</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>20</v>
+        <v>134</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>20</v>
@@ -7059,18 +6933,20 @@
         <v>20</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>325</v>
+        <v>135</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>326</v>
+        <v>136</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="N46" s="2"/>
+        <v>179</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>20</v>
@@ -7119,43 +6995,43 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>324</v>
+        <v>180</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>328</v>
+        <v>20</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>329</v>
+        <v>172</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>330</v>
+        <v>20</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>331</v>
+        <v>20</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>20</v>
+        <v>182</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7168,22 +7044,26 @@
         <v>20</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="J47" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>333</v>
+        <v>135</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>334</v>
+        <v>183</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="N47" s="2"/>
-      <c r="O47" s="2"/>
+        <v>184</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>20</v>
       </c>
@@ -7231,7 +7111,7 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>332</v>
+        <v>185</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7243,35 +7123,35 @@
         <v>20</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>300</v>
+        <v>20</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>336</v>
+        <v>132</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>337</v>
+        <v>20</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>20</v>
+        <v>335</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>88</v>
@@ -7283,19 +7163,19 @@
         <v>20</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>231</v>
+        <v>336</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>341</v>
+        <v>317</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7345,10 +7225,10 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH48" t="s" s="2">
         <v>88</v>
@@ -7360,24 +7240,24 @@
         <v>100</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>344</v>
+        <v>322</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>345</v>
+        <v>341</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7400,17 +7280,15 @@
         <v>20</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>347</v>
+        <v>215</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>350</v>
-      </c>
+        <v>344</v>
+      </c>
+      <c r="N49" s="2"/>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>20</v>
@@ -7435,13 +7313,13 @@
         <v>20</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>20</v>
+        <v>112</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>20</v>
+        <v>345</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>20</v>
+        <v>346</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>20</v>
@@ -7459,7 +7337,7 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7474,35 +7352,35 @@
         <v>100</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>342</v>
+        <v>20</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>351</v>
+        <v>172</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>352</v>
+        <v>20</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>354</v>
+        <v>20</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>20</v>
@@ -7511,20 +7389,18 @@
         <v>20</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>256</v>
+        <v>348</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>357</v>
-      </c>
+        <v>350</v>
+      </c>
+      <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>20</v>
@@ -7549,13 +7425,13 @@
         <v>20</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>166</v>
+        <v>20</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>358</v>
+        <v>20</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>359</v>
+        <v>20</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>20</v>
@@ -7573,13 +7449,13 @@
         <v>20</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>20</v>
@@ -7588,28 +7464,28 @@
         <v>100</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>360</v>
+        <v>20</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>362</v>
+        <v>20</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>363</v>
+        <v>20</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>364</v>
+        <v>352</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>364</v>
+        <v>352</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>354</v>
+        <v>20</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7625,19 +7501,19 @@
         <v>20</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>365</v>
+        <v>353</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>366</v>
+        <v>354</v>
       </c>
       <c r="M51" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="N51" t="s" s="2">
         <v>356</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>357</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7687,7 +7563,7 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>364</v>
+        <v>352</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7702,24 +7578,24 @@
         <v>100</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>360</v>
+        <v>20</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>362</v>
+        <v>20</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>363</v>
+        <v>20</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7730,7 +7606,7 @@
         <v>78</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>20</v>
@@ -7739,18 +7615,20 @@
         <v>20</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>216</v>
+        <v>167</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="N52" s="2"/>
+        <v>360</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>361</v>
+      </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>20</v>
@@ -7799,25 +7677,25 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>220</v>
+        <v>171</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>370</v>
+        <v>362</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>20</v>
@@ -7828,10 +7706,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>371</v>
+        <v>363</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>371</v>
+        <v>363</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7854,13 +7732,13 @@
         <v>20</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>222</v>
+        <v>174</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>102</v>
+        <v>175</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>103</v>
+        <v>176</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7911,7 +7789,7 @@
         <v>20</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>104</v>
+        <v>177</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7929,7 +7807,7 @@
         <v>20</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>105</v>
+        <v>172</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>20</v>
@@ -7940,14 +7818,14 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>107</v>
+        <v>134</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -7966,16 +7844,16 @@
         <v>20</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>108</v>
+        <v>135</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>109</v>
+        <v>136</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>110</v>
+        <v>179</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>111</v>
+        <v>138</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8025,7 +7903,7 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>115</v>
+        <v>180</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8037,13 +7915,13 @@
         <v>20</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>116</v>
+        <v>140</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>105</v>
+        <v>172</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>20</v>
@@ -8054,14 +7932,14 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>225</v>
+        <v>182</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8080,19 +7958,19 @@
         <v>89</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>108</v>
+        <v>135</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>226</v>
+        <v>183</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>227</v>
+        <v>184</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>111</v>
+        <v>138</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>193</v>
+        <v>144</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>20</v>
@@ -8141,7 +8019,7 @@
         <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>228</v>
+        <v>185</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8153,13 +8031,13 @@
         <v>20</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>116</v>
+        <v>140</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>186</v>
+        <v>132</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>20</v>
@@ -8170,18 +8048,18 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>375</v>
+        <v>20</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G56" t="s" s="2">
         <v>88</v>
@@ -8193,20 +8071,18 @@
         <v>20</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>376</v>
+        <v>147</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>357</v>
-      </c>
+        <v>368</v>
+      </c>
+      <c r="N56" s="2"/>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>20</v>
@@ -8255,10 +8131,10 @@
         <v>20</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH56" t="s" s="2">
         <v>88</v>
@@ -8270,24 +8146,24 @@
         <v>100</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>379</v>
+        <v>20</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>380</v>
+        <v>151</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>362</v>
+        <v>20</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>381</v>
+        <v>369</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>382</v>
+        <v>370</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>382</v>
+        <v>370</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8310,13 +8186,13 @@
         <v>20</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>256</v>
+        <v>371</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>383</v>
+        <v>372</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>384</v>
+        <v>373</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8343,13 +8219,13 @@
         <v>20</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>166</v>
+        <v>20</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>385</v>
+        <v>20</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>386</v>
+        <v>20</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>20</v>
@@ -8367,7 +8243,7 @@
         <v>20</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>382</v>
+        <v>370</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -8385,7 +8261,7 @@
         <v>20</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>105</v>
+        <v>374</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>20</v>
@@ -8396,10 +8272,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>387</v>
+        <v>375</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>387</v>
+        <v>375</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8422,13 +8298,13 @@
         <v>20</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>388</v>
+        <v>215</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>389</v>
+        <v>376</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>390</v>
+        <v>377</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8455,13 +8331,13 @@
         <v>20</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>20</v>
+        <v>112</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>20</v>
+        <v>378</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>20</v>
+        <v>379</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>20</v>
@@ -8479,7 +8355,7 @@
         <v>20</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>387</v>
+        <v>375</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8497,21 +8373,21 @@
         <v>20</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>391</v>
+        <v>380</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>20</v>
+        <v>381</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8522,7 +8398,7 @@
         <v>78</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>20</v>
@@ -8534,17 +8410,15 @@
         <v>20</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>393</v>
+        <v>215</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>394</v>
+        <v>383</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>396</v>
-      </c>
+        <v>384</v>
+      </c>
+      <c r="N59" s="2"/>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>20</v>
@@ -8569,13 +8443,13 @@
         <v>20</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>20</v>
+        <v>219</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>20</v>
+        <v>385</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>20</v>
+        <v>386</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>20</v>
@@ -8593,13 +8467,13 @@
         <v>20</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>20</v>
@@ -8611,21 +8485,21 @@
         <v>20</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>397</v>
+        <v>172</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>20</v>
+        <v>387</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8636,7 +8510,7 @@
         <v>78</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>20</v>
@@ -8648,18 +8522,20 @@
         <v>20</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>399</v>
+        <v>389</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="O60" s="2"/>
+        <v>391</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>392</v>
+      </c>
       <c r="P60" t="s" s="2">
         <v>20</v>
       </c>
@@ -8683,13 +8559,13 @@
         <v>20</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>20</v>
+        <v>219</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>20</v>
+        <v>393</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>20</v>
+        <v>394</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>20</v>
@@ -8707,39 +8583,39 @@
         <v>20</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>220</v>
+        <v>100</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>402</v>
+        <v>395</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>20</v>
+        <v>396</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8750,7 +8626,7 @@
         <v>78</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>20</v>
@@ -8762,13 +8638,13 @@
         <v>20</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>102</v>
+        <v>398</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>103</v>
+        <v>399</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -8795,13 +8671,13 @@
         <v>20</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>20</v>
+        <v>112</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>20</v>
+        <v>400</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>20</v>
+        <v>401</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>20</v>
@@ -8819,31 +8695,31 @@
         <v>20</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>104</v>
+        <v>397</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>105</v>
+        <v>402</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>20</v>
+        <v>403</v>
       </c>
     </row>
     <row r="62">
@@ -8855,7 +8731,7 @@
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>107</v>
+        <v>20</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -8874,17 +8750,15 @@
         <v>20</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>108</v>
+        <v>215</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>109</v>
+        <v>405</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>111</v>
-      </c>
+        <v>406</v>
+      </c>
+      <c r="N62" s="2"/>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>20</v>
@@ -8909,13 +8783,13 @@
         <v>20</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>20</v>
+        <v>112</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>20</v>
+        <v>407</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>20</v>
+        <v>408</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>20</v>
@@ -8933,7 +8807,7 @@
         <v>20</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>115</v>
+        <v>404</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -8945,63 +8819,59 @@
         <v>20</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>105</v>
+        <v>409</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>20</v>
+        <v>410</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>225</v>
+        <v>20</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I63" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>108</v>
+        <v>371</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>226</v>
+        <v>412</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>193</v>
-      </c>
+        <v>413</v>
+      </c>
+      <c r="N63" s="2"/>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>20</v>
       </c>
@@ -9049,39 +8919,39 @@
         <v>20</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>228</v>
+        <v>411</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>186</v>
+        <v>414</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>20</v>
+        <v>415</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>406</v>
+        <v>416</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>406</v>
+        <v>416</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9104,13 +8974,13 @@
         <v>20</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>196</v>
+        <v>215</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>407</v>
+        <v>417</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>408</v>
+        <v>418</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9137,13 +9007,13 @@
         <v>20</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>20</v>
+        <v>219</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>20</v>
+        <v>419</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>20</v>
+        <v>420</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>20</v>
@@ -9161,7 +9031,7 @@
         <v>20</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>406</v>
+        <v>416</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -9179,21 +9049,21 @@
         <v>20</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>200</v>
+        <v>421</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>409</v>
+        <v>422</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>410</v>
+        <v>423</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>410</v>
+        <v>423</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9204,7 +9074,7 @@
         <v>78</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>20</v>
@@ -9216,15 +9086,17 @@
         <v>20</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>411</v>
+        <v>167</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>412</v>
+        <v>424</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="N65" s="2"/>
+        <v>425</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>426</v>
+      </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>20</v>
@@ -9273,25 +9145,25 @@
         <v>20</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>410</v>
+        <v>423</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>100</v>
+        <v>171</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>414</v>
+        <v>427</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>20</v>
@@ -9302,10 +9174,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>415</v>
+        <v>428</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>415</v>
+        <v>428</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9328,13 +9200,13 @@
         <v>20</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>256</v>
+        <v>174</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>416</v>
+        <v>175</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>417</v>
+        <v>176</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9361,13 +9233,13 @@
         <v>20</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>166</v>
+        <v>20</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>418</v>
+        <v>20</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>419</v>
+        <v>20</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>20</v>
@@ -9385,7 +9257,7 @@
         <v>20</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>415</v>
+        <v>177</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -9397,38 +9269,38 @@
         <v>20</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>420</v>
+        <v>172</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>421</v>
+        <v>20</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>20</v>
+        <v>134</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>20</v>
@@ -9440,15 +9312,17 @@
         <v>20</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>256</v>
+        <v>135</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>423</v>
+        <v>136</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="N67" s="2"/>
+        <v>179</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>138</v>
+      </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>20</v>
@@ -9473,13 +9347,13 @@
         <v>20</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>153</v>
+        <v>20</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>425</v>
+        <v>20</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>426</v>
+        <v>20</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>20</v>
@@ -9497,43 +9371,43 @@
         <v>20</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>422</v>
+        <v>180</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>105</v>
+        <v>172</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>427</v>
+        <v>20</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>20</v>
+        <v>182</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -9546,25 +9420,25 @@
         <v>20</v>
       </c>
       <c r="I68" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>256</v>
+        <v>135</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>429</v>
+        <v>183</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>430</v>
+        <v>184</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>431</v>
+        <v>138</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>432</v>
+        <v>144</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>20</v>
@@ -9589,13 +9463,13 @@
         <v>20</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>153</v>
+        <v>20</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>433</v>
+        <v>20</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>434</v>
+        <v>20</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>20</v>
@@ -9613,7 +9487,7 @@
         <v>20</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>428</v>
+        <v>185</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -9625,27 +9499,27 @@
         <v>20</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>435</v>
+        <v>132</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>436</v>
+        <v>20</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9653,10 +9527,10 @@
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>20</v>
@@ -9668,13 +9542,13 @@
         <v>20</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>256</v>
+        <v>432</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -9701,13 +9575,13 @@
         <v>20</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>166</v>
+        <v>20</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>440</v>
+        <v>20</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>441</v>
+        <v>20</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>20</v>
@@ -9725,13 +9599,13 @@
         <v>20</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="AG69" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>20</v>
@@ -9740,24 +9614,24 @@
         <v>100</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>20</v>
+        <v>435</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>442</v>
+        <v>289</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>20</v>
+        <v>436</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>443</v>
+        <v>437</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9768,7 +9642,7 @@
         <v>78</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>20</v>
@@ -9780,15 +9654,17 @@
         <v>20</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>256</v>
+        <v>108</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="N70" s="2"/>
+        <v>440</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>441</v>
+      </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>20</v>
@@ -9813,13 +9689,13 @@
         <v>20</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>20</v>
@@ -9837,13 +9713,13 @@
         <v>20</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>20</v>
@@ -9855,21 +9731,21 @@
         <v>20</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>450</v>
+        <v>20</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9892,15 +9768,17 @@
         <v>20</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>411</v>
+        <v>215</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="N71" s="2"/>
+        <v>447</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>448</v>
+      </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>20</v>
@@ -9925,13 +9803,13 @@
         <v>20</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>20</v>
+        <v>219</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>20</v>
+        <v>449</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>20</v>
+        <v>450</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>20</v>
@@ -9949,7 +9827,7 @@
         <v>20</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -9967,21 +9845,21 @@
         <v>20</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>454</v>
+        <v>20</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>455</v>
+        <v>20</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10004,13 +9882,13 @@
         <v>20</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>256</v>
+        <v>188</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10037,13 +9915,13 @@
         <v>20</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>153</v>
+        <v>20</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>459</v>
+        <v>20</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>460</v>
+        <v>20</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>20</v>
@@ -10061,7 +9939,7 @@
         <v>20</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -10079,21 +9957,21 @@
         <v>20</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>461</v>
+        <v>282</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>462</v>
+        <v>20</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>463</v>
+        <v>454</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>463</v>
+        <v>454</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10104,7 +9982,7 @@
         <v>78</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>20</v>
@@ -10116,17 +9994,15 @@
         <v>20</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>216</v>
+        <v>455</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>464</v>
+        <v>456</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>466</v>
-      </c>
+        <v>457</v>
+      </c>
+      <c r="N73" s="2"/>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>20</v>
@@ -10175,39 +10051,39 @@
         <v>20</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>463</v>
+        <v>454</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>220</v>
+        <v>100</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>20</v>
+        <v>288</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>467</v>
+        <v>458</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>20</v>
+        <v>459</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>468</v>
+        <v>460</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>468</v>
+        <v>460</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10230,15 +10106,17 @@
         <v>20</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>222</v>
+        <v>461</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>102</v>
+        <v>462</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N74" s="2"/>
+        <v>463</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>464</v>
+      </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>20</v>
@@ -10287,7 +10165,7 @@
         <v>20</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>104</v>
+        <v>460</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -10299,926 +10177,18 @@
         <v>20</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>20</v>
+        <v>465</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>105</v>
+        <v>466</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="B75" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="C75" s="2"/>
-      <c r="D75" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="E75" s="2"/>
-      <c r="F75" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H75" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I75" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J75" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K75" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="L75" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="O75" s="2"/>
-      <c r="P75" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q75" s="2"/>
-      <c r="R75" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S75" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T75" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U75" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V75" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W75" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X75" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y75" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z75" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA75" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB75" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC75" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD75" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE75" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF75" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="AG75" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH75" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI75" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ75" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AK75" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL75" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AM75" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN75" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="B76" t="s" s="2">
-        <v>470</v>
-      </c>
-      <c r="C76" s="2"/>
-      <c r="D76" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="E76" s="2"/>
-      <c r="F76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I76" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="J76" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="K76" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="L76" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="P76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q76" s="2"/>
-      <c r="R76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF76" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="AG76" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH76" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ76" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AK76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL76" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="AM76" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN76" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="B77" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="C77" s="2"/>
-      <c r="D77" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E77" s="2"/>
-      <c r="F77" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="G77" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H77" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I77" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J77" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K77" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="L77" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="N77" s="2"/>
-      <c r="O77" s="2"/>
-      <c r="P77" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q77" s="2"/>
-      <c r="R77" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S77" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T77" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U77" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V77" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W77" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X77" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y77" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z77" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA77" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB77" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC77" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD77" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE77" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF77" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="AG77" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AH77" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI77" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ77" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK77" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="AL77" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="AM77" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="AN77" t="s" s="2">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="B78" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="C78" s="2"/>
-      <c r="D78" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E78" s="2"/>
-      <c r="F78" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G78" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H78" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I78" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J78" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K78" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="L78" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="O78" s="2"/>
-      <c r="P78" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q78" s="2"/>
-      <c r="R78" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S78" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T78" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U78" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V78" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W78" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X78" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="Y78" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="Z78" t="s" s="2">
-        <v>483</v>
-      </c>
-      <c r="AA78" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB78" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC78" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD78" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE78" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF78" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="AG78" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH78" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI78" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ78" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK78" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL78" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="AM78" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN78" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="B79" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="C79" s="2"/>
-      <c r="D79" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E79" s="2"/>
-      <c r="F79" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G79" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H79" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I79" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J79" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K79" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="L79" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="O79" s="2"/>
-      <c r="P79" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q79" s="2"/>
-      <c r="R79" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S79" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T79" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U79" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V79" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W79" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X79" t="s" s="2">
-        <v>153</v>
-      </c>
-      <c r="Y79" t="s" s="2">
-        <v>489</v>
-      </c>
-      <c r="Z79" t="s" s="2">
-        <v>490</v>
-      </c>
-      <c r="AA79" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB79" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC79" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD79" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE79" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF79" t="s" s="2">
-        <v>485</v>
-      </c>
-      <c r="AG79" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH79" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI79" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ79" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK79" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL79" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM79" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN79" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="B80" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="C80" s="2"/>
-      <c r="D80" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E80" s="2"/>
-      <c r="F80" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G80" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H80" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I80" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J80" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K80" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="L80" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="M80" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="N80" s="2"/>
-      <c r="O80" s="2"/>
-      <c r="P80" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q80" s="2"/>
-      <c r="R80" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S80" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T80" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U80" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V80" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W80" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X80" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y80" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z80" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA80" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB80" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC80" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD80" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE80" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF80" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="AG80" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH80" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI80" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ80" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK80" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL80" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="AM80" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN80" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="B81" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="C81" s="2"/>
-      <c r="D81" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E81" s="2"/>
-      <c r="F81" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G81" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H81" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I81" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J81" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K81" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="L81" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="M81" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="N81" s="2"/>
-      <c r="O81" s="2"/>
-      <c r="P81" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q81" s="2"/>
-      <c r="R81" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S81" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T81" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U81" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V81" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W81" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X81" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y81" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z81" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA81" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB81" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC81" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD81" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE81" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF81" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="AG81" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH81" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI81" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ81" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK81" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="AL81" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="AM81" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN81" t="s" s="2">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="B82" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="C82" s="2"/>
-      <c r="D82" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E82" s="2"/>
-      <c r="F82" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G82" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="H82" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I82" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J82" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K82" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="L82" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="M82" t="s" s="2">
-        <v>503</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="O82" s="2"/>
-      <c r="P82" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q82" s="2"/>
-      <c r="R82" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S82" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T82" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U82" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V82" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W82" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X82" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y82" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z82" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA82" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB82" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC82" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD82" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE82" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF82" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="AG82" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH82" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI82" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ82" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK82" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="AL82" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="AM82" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN82" t="s" s="2">
         <v>20</v>
       </c>
     </row>
